--- a/masters/master_prefecture.xlsx
+++ b/masters/master_prefecture.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$D$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$D$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -18,18 +19,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
@@ -43,7 +36,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -51,33 +44,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -440,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -450,22 +425,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>prefecture_name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>prefecture_id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>island_id</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>country_id</t>
         </is>
@@ -606,12 +581,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Kartala</t>
+          <t>Mbadjini Est</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>KM29</t>
+          <t>KM24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -628,12 +603,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Mbadjini Est</t>
+          <t>Mbadjini Ouest</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>KM24</t>
+          <t>KM25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -650,12 +625,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mbadjini Ouest</t>
+          <t>Mitsamiouli-Mboudé</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>KM25</t>
+          <t>KM26</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -672,12 +647,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mitsamiouli-Mboudé</t>
+          <t>Moroni-Bambao</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>KM26</t>
+          <t>KM27</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -694,17 +669,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Moroni-Bambao</t>
+          <t>Mrémani</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>KM27</t>
+          <t>KM12</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>KM2</t>
+          <t>KM1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -716,12 +691,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mrémani</t>
+          <t>Mutsamudu</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>KM12</t>
+          <t>KM13</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -738,17 +713,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mutsamudu</t>
+          <t>Nioumachioi</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>KM13</t>
+          <t>KM33</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>KM1</t>
+          <t>KM3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -760,17 +735,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nioumachioi</t>
+          <t>Oichili-Dimani</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>KM33</t>
+          <t>KM28</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>KM3</t>
+          <t>KM2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -782,17 +757,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Oichili-Dimani</t>
+          <t>Ouani</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>KM28</t>
+          <t>KM14</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>KM2</t>
+          <t>KM1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -804,12 +779,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ouani</t>
+          <t>Sima</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KM14</t>
+          <t>KM15</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -823,30 +798,8 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Sima</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>KM15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>KM1</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>KM</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D18"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <autoFilter ref="A1:D17"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>